--- a/docs/design-docs/05_画面設計書_対応指示・是正.xlsx
+++ b/docs/design-docs/05_画面設計書_対応指示・是正.xlsx
@@ -13,7 +13,512 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面設計書 — 対応指示登録</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>対応指示</t>
+  </si>
+  <si>
+    <t>画面ID</t>
+  </si>
+  <si>
+    <t>SCR-CTR-CREATE-001</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>対応指示登録</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-CTR-CREATE-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-CTR-CREATE-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>画面レイアウト</t>
+  </si>
+  <si>
+    <t>Header+N明細の親子構造。明細Indexed Properties(details[0].workContent形式)。各明細：作業内容/担当者(text+Popup選択)/期限/優先度。行追加(Submit→再描画)/行削除(index再振)。登録/一時保存。</t>
+  </si>
+  <si>
+    <t>画面要素一覧</t>
+  </si>
+  <si>
+    <t>要素ID</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>入力値/選択肢</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>テスト難点タグ</t>
+  </si>
+  <si>
+    <t>ctr-detail-work-{n}</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>作業内容[{n}]</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>Indexed Properties</t>
+  </si>
+  <si>
+    <t>ctr-detail-person-{n}</t>
+  </si>
+  <si>
+    <t>担当者[{n}]</t>
+  </si>
+  <si>
+    <t>読取専用</t>
+  </si>
+  <si>
+    <t>Popup選択結果</t>
+  </si>
+  <si>
+    <t>Stale Element</t>
+  </si>
+  <si>
+    <t>ctr-detail-person-btn-{n}</t>
+  </si>
+  <si>
+    <t>button</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>window.open→選択→opener反映</t>
+  </si>
+  <si>
+    <t>Window handle切替</t>
+  </si>
+  <si>
+    <t>ctr-detail-del-{n}</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>行削除→index再振</t>
+  </si>
+  <si>
+    <t>stale element</t>
+  </si>
+  <si>
+    <t>ctr-btn-add-row</t>
+  </si>
+  <si>
+    <t>+行追加</t>
+  </si>
+  <si>
+    <t>Submit→再描画</t>
+  </si>
+  <si>
+    <t>index変動→既存要素stale</t>
+  </si>
+  <si>
+    <t>Struts1マッピング</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>Action Path</t>
+  </si>
+  <si>
+    <t>/counter/create</t>
+  </si>
+  <si>
+    <t>Action Class</t>
+  </si>
+  <si>
+    <t>CounterCreateAction</t>
+  </si>
+  <si>
+    <t>Form Bean</t>
+  </si>
+  <si>
+    <t>CounterForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>counter.list / counter.create</t>
+  </si>
+  <si>
+    <t>テスト難点詳細</t>
+  </si>
+  <si>
+    <t>動的行追加(Submit→再描画)：追加後既存行stale</t>
+  </si>
+  <si>
+    <t>Indexed Properties name属性深nest</t>
+  </si>
+  <si>
+    <t>行削除後index再振：削除→追加→削除</t>
+  </si>
+  <si>
+    <t>Popup→親画面：Window handle+opener操作</t>
+  </si>
+  <si>
+    <t>画面設計書 — 対応指示一覧</t>
+  </si>
+  <si>
+    <t>SCR-CTR-LIST-001</t>
+  </si>
+  <si>
+    <t>対応指示一覧</t>
+  </si>
+  <si>
+    <t>PG-CTR-LIST-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-CTR-LIST-001</t>
+  </si>
+  <si>
+    <t>複合検索(指示日範囲×担当者×status×優先度)。一覧：指示番号/指示日/関連異常報告/優先度/明細数/完了数/全体status。印刷用表示(window.open)。CSV出力。</t>
+  </si>
+  <si>
+    <t>ctr-btn-print</t>
+  </si>
+  <si>
+    <t>印刷用表示</t>
+  </si>
+  <si>
+    <t>window.open</t>
+  </si>
+  <si>
+    <t>別window</t>
+  </si>
+  <si>
+    <t>新規window handle</t>
+  </si>
+  <si>
+    <t>ctr-btn-bulk-upd</t>
+  </si>
+  <si>
+    <t>一括status更新</t>
+  </si>
+  <si>
+    <t>confirm</t>
+  </si>
+  <si>
+    <t>テーブル列定義</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>ソート</t>
+  </si>
+  <si>
+    <t>指示番号</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>指示日</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>関連異常番号</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>完了/全明細</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>/counter/list</t>
+  </si>
+  <si>
+    <t>CounterListAction</t>
+  </si>
+  <si>
+    <t>CounterSearchForm</t>
+  </si>
+  <si>
+    <t>counter.list.tiles</t>
+  </si>
+  <si>
+    <t>印刷用別window handle切替+内容検証</t>
+  </si>
+  <si>
+    <t>完了数/全明細数表示更新</t>
+  </si>
+  <si>
+    <t>画面設計書 — 対応指示詳細・完了報告</t>
+  </si>
+  <si>
+    <t>SCR-CTR-DETAIL-001</t>
+  </si>
+  <si>
+    <t>対応指示詳細・完了報告</t>
+  </si>
+  <si>
+    <t>PG-CTR-DETAIL-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-CTR-DETAIL-001</t>
+  </si>
+  <si>
+    <t>指示header+明細一覧。各行完了報告button→実績時間/使用部品/使用量/所見入力行展開。全明細完了→header自動完了。使用部品→在庫超えalert。</t>
+  </si>
+  <si>
+    <t>ctr-dtl-btn-complete-{n}</t>
+  </si>
+  <si>
+    <t>完了報告</t>
+  </si>
+  <si>
+    <t>押下→入力行展開</t>
+  </si>
+  <si>
+    <t>DOM追加</t>
+  </si>
+  <si>
+    <t>ctr-dtl-actual-hours-{n}</t>
+  </si>
+  <si>
+    <t>実績作業時間</t>
+  </si>
+  <si>
+    <t>数値(時間)</t>
+  </si>
+  <si>
+    <t>完了時必須</t>
+  </si>
+  <si>
+    <t>条件付必須</t>
+  </si>
+  <si>
+    <t>ctr-dtl-used-part-{n}</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>使用部品</t>
+  </si>
+  <si>
+    <t>部品master</t>
+  </si>
+  <si>
+    <t>在庫超えalert</t>
+  </si>
+  <si>
+    <t>ctr-dtl-header-status</t>
+  </si>
+  <si>
+    <t>全体status</t>
+  </si>
+  <si>
+    <t>自動計算</t>
+  </si>
+  <si>
+    <t>全明細完了→自動完了</t>
+  </si>
+  <si>
+    <t>/counter/detail</t>
+  </si>
+  <si>
+    <t>CounterDetailAction</t>
+  </si>
+  <si>
+    <t>CounterDetailForm</t>
+  </si>
+  <si>
+    <t>counter.list / counter.detail</t>
+  </si>
+  <si>
+    <t>明細個別完了報告→DOM展開</t>
+  </si>
+  <si>
+    <t>全明細完了→header自動完了trigger</t>
+  </si>
+  <si>
+    <t>部品選択→在庫超え条件付表示</t>
+  </si>
+  <si>
+    <t>画面設計書 — 是正処置報告書</t>
+  </si>
+  <si>
+    <t>是正処置</t>
+  </si>
+  <si>
+    <t>SCR-CTR-CAPA-001</t>
+  </si>
+  <si>
+    <t>是正処置報告書</t>
+  </si>
+  <si>
+    <t>PG-CTR-CAPA-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-CTR-CAPA-001</t>
+  </si>
+  <si>
+    <t>異常報告引継表示。なぜなぜ分析5段階(textarea×5)。再発防止策/効果確認方法/効果確認期限。承認申請。</t>
+  </si>
+  <si>
+    <t>capa-why{1-5}</t>
+  </si>
+  <si>
+    <t>textarea</t>
+  </si>
+  <si>
+    <t>なぜ①〜⑤</t>
+  </si>
+  <si>
+    <t>必須×5</t>
+  </si>
+  <si>
+    <t>capa-countermeasure</t>
+  </si>
+  <si>
+    <t>再発防止策</t>
+  </si>
+  <si>
+    <t>capa-verify-method</t>
+  </si>
+  <si>
+    <t>効果確認方法</t>
+  </si>
+  <si>
+    <t>capa-verify-date</t>
+  </si>
+  <si>
+    <t>効果確認期限</t>
+  </si>
+  <si>
+    <t>YYYYMMDD</t>
+  </si>
+  <si>
+    <t>必須 未来日</t>
+  </si>
+  <si>
+    <t>/counter/capa/create</t>
+  </si>
+  <si>
+    <t>CapaAction</t>
+  </si>
+  <si>
+    <t>CapaForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>counter.list / counter.capa</t>
+  </si>
+  <si>
+    <t>なぜなぜ5段階：各段入力値検証</t>
+  </si>
+  <si>
+    <t>全textarea必須validation</t>
+  </si>
+  <si>
+    <t>異常報告→是正data引継</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
